--- a/Behind/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/Behind/july 2026/Daily Reports/LMT Orders.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Behind\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B174802D-6ACE-4AD2-ABE2-71649F2CF34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98E7F82-B337-468D-B55C-E9A0D1EF9E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2019,114 +2019,114 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2663,14 +2663,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="181">
+      <c r="B1" s="184">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
-      </c>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
+        <v>46238</v>
+      </c>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="184"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2692,10 +2692,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="178" t="s">
+      <c r="A2" s="181" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="182" t="s">
+      <c r="B2" s="185" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2728,13 +2728,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="170"/>
-      <c r="N2" s="171"/>
-      <c r="O2" s="172"/>
-      <c r="P2" s="173" t="s">
+      <c r="M2" s="173"/>
+      <c r="N2" s="174"/>
+      <c r="O2" s="175"/>
+      <c r="P2" s="176" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="174"/>
+      <c r="Q2" s="177"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2753,8 +2753,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="178"/>
-      <c r="B3" s="183"/>
+      <c r="A3" s="181"/>
+      <c r="B3" s="186"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2785,29 +2785,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="175" t="s">
+      <c r="M3" s="178" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="176"/>
-      <c r="O3" s="177"/>
+      <c r="N3" s="179"/>
+      <c r="O3" s="180"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="185" t="s">
+      <c r="R3" s="188" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="186"/>
-      <c r="T3" s="186"/>
-      <c r="U3" s="187"/>
-      <c r="V3" s="188" t="s">
+      <c r="S3" s="189"/>
+      <c r="T3" s="189"/>
+      <c r="U3" s="190"/>
+      <c r="V3" s="191" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="189"/>
-      <c r="X3" s="189"/>
-      <c r="Y3" s="190"/>
+      <c r="W3" s="192"/>
+      <c r="X3" s="192"/>
+      <c r="Y3" s="193"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="178"/>
-      <c r="B4" s="184"/>
+      <c r="A4" s="181"/>
+      <c r="B4" s="187"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -9803,30 +9803,30 @@
       <c r="B94" s="165">
         <v>90</v>
       </c>
-      <c r="C94" s="202" t="s">
+      <c r="C94" s="168" t="s">
         <v>216</v>
       </c>
-      <c r="D94" s="203">
+      <c r="D94" s="169">
         <v>160</v>
       </c>
-      <c r="E94" s="203"/>
-      <c r="F94" s="203"/>
-      <c r="G94" s="203">
+      <c r="E94" s="169"/>
+      <c r="F94" s="169"/>
+      <c r="G94" s="169">
         <v>160</v>
       </c>
-      <c r="H94" s="203">
+      <c r="H94" s="169">
         <v>160</v>
       </c>
-      <c r="I94" s="204">
+      <c r="I94" s="170">
         <v>160</v>
       </c>
-      <c r="J94" s="203">
+      <c r="J94" s="169">
         <v>160</v>
       </c>
-      <c r="K94" s="203">
+      <c r="K94" s="169">
         <v>160</v>
       </c>
-      <c r="L94" s="203">
+      <c r="L94" s="169">
         <v>160</v>
       </c>
       <c r="M94" s="167">
@@ -12472,10 +12472,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="191" t="s">
+      <c r="B132" s="194" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="192"/>
+      <c r="C132" s="195"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -12739,10 +12739,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="179" t="s">
+      <c r="B136" s="182" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="180"/>
+      <c r="C136" s="183"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -12833,10 +12833,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="168" t="s">
+      <c r="B137" s="171" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="169"/>
+      <c r="C137" s="172"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -12974,25 +12974,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="195" t="s">
+      <c r="C3" s="198" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="196"/>
-      <c r="E3" s="196"/>
-      <c r="F3" s="196"/>
-      <c r="G3" s="197"/>
-      <c r="H3" s="199" t="s">
+      <c r="D3" s="199"/>
+      <c r="E3" s="199"/>
+      <c r="F3" s="199"/>
+      <c r="G3" s="200"/>
+      <c r="H3" s="202" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="200"/>
-      <c r="K3" s="201" t="s">
+      <c r="I3" s="203"/>
+      <c r="K3" s="204" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="201"/>
-      <c r="M3" s="201"/>
-      <c r="N3" s="201"/>
-      <c r="O3" s="201"/>
-      <c r="P3" s="201"/>
+      <c r="L3" s="204"/>
+      <c r="M3" s="204"/>
+      <c r="N3" s="204"/>
+      <c r="O3" s="204"/>
+      <c r="P3" s="204"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
@@ -13315,14 +13315,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="198" t="s">
+      <c r="C11" s="201" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="198"/>
-      <c r="F11" s="198" t="s">
+      <c r="D11" s="201"/>
+      <c r="F11" s="201" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="198"/>
+      <c r="G11" s="201"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -13424,10 +13424,10 @@
         <f>G12*40</f>
         <v>305360</v>
       </c>
-      <c r="S13" s="193" t="s">
+      <c r="S13" s="196" t="s">
         <v>152</v>
       </c>
-      <c r="T13" s="193"/>
+      <c r="T13" s="196"/>
       <c r="U13" s="141">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -13543,13 +13543,13 @@
       </c>
     </row>
     <row r="20" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="194" t="s">
+      <c r="D20" s="197" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="194"/>
-      <c r="F20" s="194"/>
-      <c r="G20" s="194"/>
-      <c r="H20" s="194"/>
+      <c r="E20" s="197"/>
+      <c r="F20" s="197"/>
+      <c r="G20" s="197"/>
+      <c r="H20" s="197"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
